--- a/data/sites/manufacturing/Quality Assurance/gauge-and-equipment-calibration-schedule.xlsx
+++ b/data/sites/manufacturing/Quality Assurance/gauge-and-equipment-calibration-schedule.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gauge and Equipment Calibration Schedule</t>
+          <t>Gauge and Equipment Calibration Schedule - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,107 +651,2261 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 1 (Executive Summary &amp; Scope) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Calibration intervals are set by equipment type and criticality to product quality. Secondary control 1.2: Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Last Calibrated</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Next Due</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Caliper Set A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMM Station</t>
+          <t>Caliper Set A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quality Lab</t>
+          <t>Line 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Torque Wrench 7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Line 3 Station 7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2027-01-20</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 10 (Cross-Functional Dependencies) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Equipment past due for calibration is removed from service and tagged. Secondary control 10.2: External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 11 (Continuous Improvement Roadmap) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: External calibration vendors are audited annually against ISO 17025 accreditation. Secondary control 11.2: Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: Calibration records are retained for the life of the equipment plus three years. Secondary control 12.2: Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 2 (Architecture &amp; Process Flow) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Equipment past due for calibration is removed from service and tagged. Secondary control 2.2: External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 3 (Governance Standards &amp; Controls) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: External calibration vendors are audited annually against ISO 17025 accreditation. Secondary control 3.2: Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 4 (Operational KPIs &amp; Benchmarks) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: Calibration records are retained for the life of the equipment plus three years. Secondary control 4.2: Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 5 (Roles, Responsibilities &amp; RACI) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Calibration intervals are set by equipment type and criticality to product quality. Secondary control 5.2: Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 6 (Standard Operating Procedures) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Equipment past due for calibration is removed from service and tagged. Secondary control 6.2: External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 7 (Risk Register &amp; Mitigations) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: External calibration vendors are audited annually against ISO 17025 accreditation. Secondary control 7.2: Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 8 (Quality Assurance &amp; Audits) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: Calibration records are retained for the life of the equipment plus three years. Secondary control 8.2: Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gauge and Equipment Calibration Schedule - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 9 (Exception Handling &amp; Escalations) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Calibration intervals are set by equipment type and criticality to product quality. Secondary control 9.2: Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Last Calibrated</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Next Due</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caliper Set A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CMM Station</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quality Lab</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Torque Wrench 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line 3 Station 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Equipment past due for calibration is removed from service and tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/sites/manufacturing/Quality Assurance/gauge-and-equipment-calibration-schedule.xlsx
+++ b/data/sites/manufacturing/Quality Assurance/gauge-and-equipment-calibration-schedule.xlsx
@@ -16,9 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Sign-off" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,36 +278,6 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -810,7 +778,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gauge and Equipment Calibration Schedule - Section 10: Cross-Functional Dependencies</t>
+          <t>Gauge and Equipment Calibration Schedule - Section 10: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -824,7 +792,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 10 (Cross-Functional Dependencies) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Documents upstream and downstream team dependencies and service-level commitments.</t>
+          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 10 (Appendix, Lineage &amp; Sign-off) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
@@ -970,391 +938,6 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>• Section 10 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gauge and Equipment Calibration Schedule - Section 11: Continuous Improvement Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 11 (Continuous Improvement Roadmap) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 11.1: External calibration vendors are audited annually against ISO 17025 accreditation. Secondary control 11.2: Calibration records are retained for the life of the equipment plus three years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Last Calibrated</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Next Due</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Caliper Set A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CMM Station</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Quality Lab</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Torque Wrench 7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Line 3 Station 7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-11</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Quality Lab</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 11 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• External calibration vendors are audited annually against ISO 17025 accreditation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 11 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gauge and Equipment Calibration Schedule - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Manufacturing Knowledge Hub | Quality Assurance | Owner: Linda Park  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Master schedule of calibration due dates for measurement equipment used across the quality lab and production floor. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Quality Assurance within Manufacturing Knowledge Hub and is maintained by Linda Park. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: Calibration records are retained for the life of the equipment plus three years. Secondary control 12.2: Calibration intervals are set by equipment type and criticality to product quality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Last Calibrated</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Next Due</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Caliper Set A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CMM Station</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Quality Lab</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Torque Wrench 7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Line 3 Station 7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Line 3 Station 7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Calibration records are retained for the life of the equipment plus three years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Calibration intervals are set by equipment type and criticality to product quality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Linda Park under Quality Assurance governance.</t>
         </is>
       </c>
     </row>
